--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-13T00:31:17+00:00</t>
+          <t>2026-09-14T00:33:55+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-14T00:33:55+00:00</t>
+          <t>2026-09-15T01:07:14+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15T01:07:14+00:00</t>
+          <t>2026-09-16T00:55:23+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-16T00:55:23+00:00</t>
+          <t>2026-09-17T02:24:51+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-17T02:24:51+00:00</t>
+          <t>2026-09-18T00:56:14+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-18T00:56:14+00:00</t>
+          <t>2026-09-19T00:50:40+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-19T00:50:40+00:00</t>
+          <t>2026-09-20T00:32:54+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-20T00:32:54+00:00</t>
+          <t>2026-09-21T00:43:05+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-21T00:43:05+00:00</t>
+          <t>2026-09-22T01:25:10+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-22T01:25:10+00:00</t>
+          <t>2026-09-23T01:06:45+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-23T01:06:45+00:00</t>
+          <t>2026-09-24T01:01:44+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-24T01:01:44+00:00</t>
+          <t>2026-09-25T01:03:18+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-25T01:03:18+00:00</t>
+          <t>2026-09-26T01:06:03+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-26T01:06:03+00:00</t>
+          <t>2026-09-27T01:03:31+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-27T01:03:31+00:00</t>
+          <t>2026-09-28T01:22:19+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-28T01:22:19+00:00</t>
+          <t>2026-09-29T02:27:14+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29T02:27:14+00:00</t>
+          <t>2026-09-30T01:46:25+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-30T01:46:25+00:00</t>
+          <t>2026-10-01T01:44:47+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-01T01:44:47+00:00</t>
+          <t>2026-10-02T01:54:51+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02T01:54:51+00:00</t>
+          <t>2026-10-03T01:37:52+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-03T01:37:52+00:00</t>
+          <t>2026-10-04T02:18:21+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-04T02:18:21+00:00</t>
+          <t>2026-10-05T01:26:53+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-05T01:26:53+00:00</t>
+          <t>2026-10-06T02:37:38+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06T02:37:38+00:00</t>
+          <t>2026-10-07T01:55:56+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-07T01:55:56+00:00</t>
+          <t>2026-10-08T02:24:02+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-08T02:24:02+00:00</t>
+          <t>2026-10-09T02:42:22+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-09T02:42:22+00:00</t>
+          <t>2026-10-10T02:01:51+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-10T02:01:51+00:00</t>
+          <t>2026-10-10T09:16:31+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-10T09:16:31+00:00</t>
+          <t>2026-10-10T16:04:15+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-10T16:04:15+00:00</t>
+          <t>2026-10-10T22:08:57+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-10T22:08:57+00:00</t>
+          <t>2026-10-11T01:26:50+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-11T01:26:50+00:00</t>
+          <t>2026-10-11T09:33:39+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-11T09:33:39+00:00</t>
+          <t>2026-10-11T16:30:01+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-11T16:30:01+00:00</t>
+          <t>2026-10-11T22:37:41+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-11T22:37:41+00:00</t>
+          <t>2026-10-12T01:57:19+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-12T01:57:19+00:00</t>
+          <t>2026-10-12T10:03:36+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-12T10:03:36+00:00</t>
+          <t>2026-10-12T20:05:35+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-12T20:05:35+00:00</t>
+          <t>2026-10-13T03:19:00+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-13T03:19:00+00:00</t>
+          <t>2026-10-13T14:44:04+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-13T14:44:04+00:00</t>
+          <t>2026-10-13T20:29:06+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-13T20:29:06+00:00</t>
+          <t>2026-10-14T01:31:29+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14T01:31:29+00:00</t>
+          <t>2026-10-14T08:16:22+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14T08:16:22+00:00</t>
+          <t>2026-10-14T15:40:30+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14T15:40:30+00:00</t>
+          <t>2026-10-14T22:00:59+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14T22:00:59+00:00</t>
+          <t>2026-10-15T01:09:43+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-15T01:09:43+00:00</t>
+          <t>2026-10-15T07:53:58+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-15T07:53:58+00:00</t>
+          <t>2026-10-15T15:26:51+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-15T15:26:51+00:00</t>
+          <t>2026-10-15T21:54:38+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-15T21:54:38+00:00</t>
+          <t>2026-10-16T00:56:26+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-16T00:56:26+00:00</t>
+          <t>2026-10-16T07:45:32+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-16T07:45:32+00:00</t>
+          <t>2026-10-16T15:06:28+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-16T15:06:28+00:00</t>
+          <t>2026-10-16T21:52:34+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-16T21:52:34+00:00</t>
+          <t>2026-10-17T00:56:40+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-17T00:56:40+00:00</t>
+          <t>2026-10-17T07:22:50+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-17T07:22:50+00:00</t>
+          <t>2026-10-17T14:02:56+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-17T14:02:56+00:00</t>
+          <t>2026-10-17T17:42:20+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-17T17:42:20+00:00</t>
+          <t>2026-10-17T21:11:20+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-17T21:11:20+00:00</t>
+          <t>2026-10-18T00:31:56+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-18T00:31:56+00:00</t>
+          <t>2026-10-18T07:36:58+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-18T07:36:58+00:00</t>
+          <t>2026-10-18T14:14:57+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-18T14:14:57+00:00</t>
+          <t>2026-10-18T17:43:18+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-18T17:43:18+00:00</t>
+          <t>2026-10-18T21:13:23+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-18T21:13:23+00:00</t>
+          <t>2026-10-19T00:38:45+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-19T00:38:45+00:00</t>
+          <t>2026-10-19T08:20:51+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-19T08:20:51+00:00</t>
+          <t>2026-10-19T17:18:14+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-19T17:18:14+00:00</t>
+          <t>2026-10-19T22:43:37+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-19T22:43:37+00:00</t>
+          <t>2026-10-20T01:23:47+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-20T01:23:47+00:00</t>
+          <t>2026-10-20T08:04:55+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-20T08:04:55+00:00</t>
+          <t>2026-10-20T15:31:15+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-20T15:31:15+00:00</t>
+          <t>2026-10-20T22:01:28+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-20T22:01:28+00:00</t>
+          <t>2026-10-21T01:10:32+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-21T01:10:32+00:00</t>
+          <t>2026-10-21T08:10:20+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-21T08:10:20+00:00</t>
+          <t>2026-10-21T15:47:10+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-21T15:47:10+00:00</t>
+          <t>2026-10-21T22:04:13+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-21T22:04:13+00:00</t>
+          <t>2026-10-22T01:07:19+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-22T01:07:19+00:00</t>
+          <t>2026-10-22T08:10:27+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-22T08:10:27+00:00</t>
+          <t>2026-10-22T15:46:17+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-22T15:46:17+00:00</t>
+          <t>2026-10-22T22:01:32+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-22T22:01:32+00:00</t>
+          <t>2026-10-23T01:08:16+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-23T01:08:16+00:00</t>
+          <t>2026-10-23T08:09:10+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-23T08:09:10+00:00</t>
+          <t>2026-10-23T15:34:24+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-23T15:34:24+00:00</t>
+          <t>2026-10-23T21:49:10+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-23T21:49:10+00:00</t>
+          <t>2026-10-24T01:17:20+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-24T01:17:20+00:00</t>
+          <t>2026-10-24T07:47:43+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-24T07:47:43+00:00</t>
+          <t>2026-10-24T09:10:08+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-24T09:10:08+00:00</t>
+          <t>2026-10-24T14:12:38+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-24T14:12:38+00:00</t>
+          <t>2026-10-24T15:23:18+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-24T15:23:18+00:00</t>
+          <t>2026-10-24T17:44:43+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-24T17:44:43+00:00</t>
+          <t>2026-10-24T21:21:18+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-24T21:21:18+00:00</t>
+          <t>2026-10-25T00:43:08+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25T00:43:08+00:00</t>
+          <t>2026-10-25T07:57:56+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25T07:57:56+00:00</t>
+          <t>2026-10-25T14:43:12+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25T14:43:12+00:00</t>
+          <t>2026-10-25T18:01:02+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25T18:01:02+00:00</t>
+          <t>2026-10-25T21:26:05+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25T21:26:05+00:00</t>
+          <t>2026-10-26T00:57:25+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-26T00:57:25+00:00</t>
+          <t>2026-10-26T08:29:19+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-26T08:29:19+00:00</t>
+          <t>2026-10-26T17:05:28+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-26T17:05:28+00:00</t>
+          <t>2026-10-26T22:58:21+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-26T22:58:21+00:00</t>
+          <t>2026-10-27T01:45:10+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27T01:45:10+00:00</t>
+          <t>2026-10-27T01:48:16+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27T01:48:16+00:00</t>
+          <t>2026-10-27T08:32:14+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27T08:32:14+00:00</t>
+          <t>2026-10-27T16:08:29+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27T16:08:29+00:00</t>
+          <t>2026-10-27T22:47:15+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27T22:47:15+00:00</t>
+          <t>2026-10-28T01:56:36+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-28T01:56:36+00:00</t>
+          <t>2026-10-28T09:11:42+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-28T09:11:42+00:00</t>
+          <t>2026-10-28T16:56:08+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-28T16:56:08+00:00</t>
+          <t>2026-10-28T22:55:58+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-28T22:55:58+00:00</t>
+          <t>2026-10-29T02:01:25+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29T02:01:25+00:00</t>
+          <t>2026-10-29T06:41:36+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29T06:41:36+00:00</t>
+          <t>2026-10-29T09:09:42+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29T09:09:42+00:00</t>
+          <t>2026-10-29T17:13:41+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29T17:13:41+00:00</t>
+          <t>2026-10-29T23:04:06+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29T23:04:06+00:00</t>
+          <t>2026-10-30T02:17:21+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30T02:17:21+00:00</t>
+          <t>2026-10-30T09:20:40+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30T09:20:40+00:00</t>
+          <t>2026-10-30T16:54:53+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30T16:54:53+00:00</t>
+          <t>2026-10-30T22:45:13+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30T22:45:13+00:00</t>
+          <t>2026-10-31T01:56:33+00:00</t>
         </is>
       </c>
     </row>
